--- a/Apostas_Diarias/Apostas_20260425.xlsx
+++ b/Apostas_Diarias/Apostas_20260425.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/DASHBOARD_ARKAD-1/Apostas_Diarias/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_23192D5295D647565D60C4F0505ED87656CDE63D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21AAC642-AF3D-4C71-9CB6-751F1F5919B1}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_2B590F4F95E64144EDE3C2F0502B18F36B83E744" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{130E6BEC-4783-4E63-B103-1F3043776DA5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Data</t>
   </si>
@@ -86,33 +86,6 @@
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Grenoble x Le Mans</t>
-  </si>
-  <si>
-    <t>09:45:00</t>
-  </si>
-  <si>
-    <t>POLAND 1</t>
-  </si>
-  <si>
-    <t>Korona Kielce x GKS Katowice</t>
-  </si>
-  <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
-    <t>BULGARIA 1</t>
-  </si>
-  <si>
-    <t>CSKA Sofia x PFC Levski Sofia</t>
-  </si>
-  <si>
     <t>11:00:00</t>
   </si>
   <si>
@@ -122,42 +95,6 @@
     <t>Airdrieonians x Ayr</t>
   </si>
   <si>
-    <t>CZECH 1</t>
-  </si>
-  <si>
-    <t>Banik Ostrava x Plzen</t>
-  </si>
-  <si>
-    <t>Bohemians 1905 x Sparta Prague</t>
-  </si>
-  <si>
-    <t>FK Jablonec x Slovan Liberec</t>
-  </si>
-  <si>
-    <t>NORWAY 1</t>
-  </si>
-  <si>
-    <t>Fredrikstad x Viking</t>
-  </si>
-  <si>
-    <t>Teplice x Hradec Kralove</t>
-  </si>
-  <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 1</t>
-  </si>
-  <si>
-    <t>Tondela x CD Nacional Funchal</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>Lechia Gdansk x Rakow Czestochowa</t>
-  </si>
-  <si>
     <t>13:00:00</t>
   </si>
   <si>
@@ -179,12 +116,6 @@
     <t>KFC Komarno x MFk Skalica</t>
   </si>
   <si>
-    <t>NORWAY 2</t>
-  </si>
-  <si>
-    <t>Strommen x Kongsvinger</t>
-  </si>
-  <si>
     <t>Zemplin x Podbrezova</t>
   </si>
   <si>
@@ -197,46 +128,7 @@
     <t>Burgos x Deportivo</t>
   </si>
   <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 1</t>
-  </si>
-  <si>
-    <t>Angers x Paris St-G</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Felgueiras x Leiria</t>
-  </si>
-  <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>CFR Cluj x Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>NETHERLANDS 1</t>
-  </si>
-  <si>
-    <t>NAC Breda x Ajax</t>
-  </si>
-  <si>
     <t>15:30:00</t>
-  </si>
-  <si>
-    <t>USA 1</t>
-  </si>
-  <si>
-    <t>CF Montreal x New York City</t>
   </si>
   <si>
     <t>Thun x Lugano</t>
@@ -594,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -705,21 +597,21 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I3">
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J28" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J12" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K28" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>49.210526315789473</v>
+        <f t="shared" ref="K3:K12" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>40.652173913043484</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -745,10 +637,10 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>500</v>
@@ -759,7 +651,7 @@
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>27.5</v>
+        <v>58.4375</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -773,22 +665,22 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <v>500</v>
@@ -799,7 +691,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -813,22 +705,22 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="I6">
         <v>500</v>
@@ -839,7 +731,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <v>28.333333333333336</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -853,36 +745,36 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>500</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>RED</v>
+        <v>GREEN</v>
       </c>
       <c r="K7">
         <f t="shared" si="1"/>
-        <v>-500</v>
+        <v>27.5</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -893,22 +785,22 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>500</v>
@@ -919,7 +811,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>54.360465116279073</v>
+        <v>58.4375</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -933,10 +825,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
@@ -945,24 +837,24 @@
         <v>16</v>
       </c>
       <c r="G9">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="H9">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I9">
         <v>500</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <v>RED</v>
       </c>
       <c r="K9">
         <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <v>-500</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -970,25 +862,25 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="H10">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="I10">
         <v>500</v>
@@ -999,7 +891,7 @@
       </c>
       <c r="K10">
         <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
+        <v>61.513157894736842</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1010,39 +902,39 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G11">
-        <v>9.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H11">
-        <v>9.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I11">
         <v>500</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="0"/>
-        <v>RED</v>
+        <v>GREEN</v>
       </c>
       <c r="K11">
         <f t="shared" si="1"/>
-        <v>-500</v>
+        <v>64.930555555555557</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1050,25 +942,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
         <v>37</v>
       </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
       <c r="G12">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="H12">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="I12">
         <v>500</v>
@@ -1079,649 +971,9 @@
       </c>
       <c r="K12">
         <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
+        <v>73.046875</v>
       </c>
       <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>18</v>
-      </c>
-      <c r="H13">
-        <v>18</v>
-      </c>
-      <c r="I13">
-        <v>500</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>9</v>
-      </c>
-      <c r="H14">
-        <v>9</v>
-      </c>
-      <c r="I14">
-        <v>500</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>26</v>
-      </c>
-      <c r="H15">
-        <v>26</v>
-      </c>
-      <c r="I15">
-        <v>500</v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>18.700000000000003</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>17.5</v>
-      </c>
-      <c r="H16">
-        <v>17.5</v>
-      </c>
-      <c r="I16">
-        <v>500</v>
-      </c>
-      <c r="J16" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>28.333333333333336</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>14.5</v>
-      </c>
-      <c r="H17">
-        <v>14.5</v>
-      </c>
-      <c r="I17">
-        <v>500</v>
-      </c>
-      <c r="J17" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>34.629629629629626</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18">
-        <v>18</v>
-      </c>
-      <c r="H18">
-        <v>18</v>
-      </c>
-      <c r="I18">
-        <v>500</v>
-      </c>
-      <c r="J18" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19">
-        <v>9</v>
-      </c>
-      <c r="H19">
-        <v>9</v>
-      </c>
-      <c r="I19">
-        <v>500</v>
-      </c>
-      <c r="J19" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20">
-        <v>10.5</v>
-      </c>
-      <c r="H20">
-        <v>10.5</v>
-      </c>
-      <c r="I20">
-        <v>500</v>
-      </c>
-      <c r="J20" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21">
-        <v>10.5</v>
-      </c>
-      <c r="H21">
-        <v>10.5</v>
-      </c>
-      <c r="I21">
-        <v>500</v>
-      </c>
-      <c r="J21" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22">
-        <v>12</v>
-      </c>
-      <c r="H22">
-        <v>12</v>
-      </c>
-      <c r="I22">
-        <v>500</v>
-      </c>
-      <c r="J22" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23">
-        <v>11</v>
-      </c>
-      <c r="H23">
-        <v>11</v>
-      </c>
-      <c r="I23">
-        <v>500</v>
-      </c>
-      <c r="J23" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>46.75</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24">
-        <v>12</v>
-      </c>
-      <c r="H24">
-        <v>12</v>
-      </c>
-      <c r="I24">
-        <v>500</v>
-      </c>
-      <c r="J24" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25">
-        <v>20</v>
-      </c>
-      <c r="H25">
-        <v>20</v>
-      </c>
-      <c r="I25">
-        <v>500</v>
-      </c>
-      <c r="J25" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26">
-        <v>8.6</v>
-      </c>
-      <c r="H26">
-        <v>8.6</v>
-      </c>
-      <c r="I26">
-        <v>500</v>
-      </c>
-      <c r="J26" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="1"/>
-        <v>61.513157894736842</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="H27">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I27">
-        <v>500</v>
-      </c>
-      <c r="J27" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="1"/>
-        <v>64.930555555555557</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28">
-        <v>7.4</v>
-      </c>
-      <c r="H28">
-        <v>7.4</v>
-      </c>
-      <c r="I28">
-        <v>500</v>
-      </c>
-      <c r="J28" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="1"/>
-        <v>73.046875</v>
-      </c>
-      <c r="L28">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260425.xlsx
+++ b/Apostas_Diarias/Apostas_20260425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_2B590F4F95E64144EDE3C2F0502B18F36B83E744" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{130E6BEC-4783-4E63-B103-1F3043776DA5}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F95D64F0A0101DBF050F9A0724079E07D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C04359C-725F-417C-92D2-DE3822BB2A75}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
   <si>
     <t>Data</t>
   </si>
@@ -74,25 +74,46 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>08:00:00</t>
-  </si>
-  <si>
-    <t>GERMANY 2</t>
-  </si>
-  <si>
-    <t>Preussen Munster x Arminia Bielefeld</t>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>FRANCE 2</t>
+  </si>
+  <si>
+    <t>Grenoble x Le Mans</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
+    <t>FINLAND 1</t>
+  </si>
+  <si>
+    <t>Lahti x AC Oulu</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>BULGARIA 1</t>
+  </si>
+  <si>
+    <t>CSKA Sofia x PFC Levski Sofia</t>
+  </si>
+  <si>
     <t>11:00:00</t>
   </si>
   <si>
     <t>SCOTLAND 2</t>
   </si>
   <si>
-    <t>Airdrieonians x Ayr</t>
+    <t>Arbroath x Partick</t>
+  </si>
+  <si>
+    <t>NORWAY 1</t>
+  </si>
+  <si>
+    <t>Fredrikstad x Viking</t>
   </si>
   <si>
     <t>13:00:00</t>
@@ -104,37 +125,19 @@
     <t>Bologna x Roma</t>
   </si>
   <si>
-    <t>SWITZERLAND 1</t>
-  </si>
-  <si>
-    <t>Grasshoppers Zurich x Luzern</t>
-  </si>
-  <si>
-    <t>SLOVAKIA 1</t>
-  </si>
-  <si>
-    <t>KFC Komarno x MFk Skalica</t>
-  </si>
-  <si>
-    <t>Zemplin x Podbrezova</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>SPAIN 2</t>
-  </si>
-  <si>
-    <t>Burgos x Deportivo</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>Thun x Lugano</t>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Felgueiras x Leiria</t>
   </si>
   <si>
     <t>P2</t>
+  </si>
+  <si>
+    <t>Queens Park x Dunfermline</t>
   </si>
   <si>
     <t>15:45:00</t>
@@ -486,14 +489,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -536,6 +539,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -557,12 +563,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <f>G2</f>
+        <v>10.5</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -571,7 +579,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>40.652173913043484</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -585,33 +593,35 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="H3">
-        <v>12.5</v>
+        <f t="shared" ref="H3:H11" si="0">G3</f>
+        <v>10.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I11" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J12" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J11" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K12" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>40.652173913043484</v>
+        <f t="shared" ref="K3:K11" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>49.210526315789473</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -625,33 +635,35 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -665,7 +677,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -677,21 +689,23 @@
         <v>16</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>18.700000000000003</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -705,7 +719,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -717,21 +731,23 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="H6">
-        <v>17.5</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I6">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>28.333333333333336</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -745,33 +761,35 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I7">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
+        <f t="shared" si="3"/>
+        <v>58.4375</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -785,33 +803,35 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I8">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>58.4375</v>
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -822,39 +842,41 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="I9">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
-        <v>-500</v>
+        <f t="shared" si="3"/>
+        <v>63.175675675675684</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -865,13 +887,13 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -880,17 +902,19 @@
         <v>8.6</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
         <v>8.6</v>
       </c>
       <c r="I10">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>61.513157894736842</v>
       </c>
       <c r="L10">
@@ -902,78 +926,40 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11">
-        <v>8.1999999999999993</v>
+        <v>7.4</v>
       </c>
       <c r="H11">
-        <v>8.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>7.4</v>
       </c>
       <c r="I11">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
-        <v>64.930555555555557</v>
+        <f t="shared" si="3"/>
+        <v>73.046875</v>
       </c>
       <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12">
-        <v>7.4</v>
-      </c>
-      <c r="H12">
-        <v>7.4</v>
-      </c>
-      <c r="I12">
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>73.046875</v>
-      </c>
-      <c r="L12">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260425.xlsx
+++ b/Apostas_Diarias/Apostas_20260425.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F95D64F0A0101DBF050F9A0724079E07D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C04359C-725F-417C-92D2-DE3822BB2A75}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_2B590F4F95E64144EDE3C2F0502B18F36B83E744" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{130E6BEC-4783-4E63-B103-1F3043776DA5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Data</t>
   </si>
@@ -74,46 +74,25 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Grenoble x Le Mans</t>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>GERMANY 2</t>
+  </si>
+  <si>
+    <t>Preussen Munster x Arminia Bielefeld</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>FINLAND 1</t>
-  </si>
-  <si>
-    <t>Lahti x AC Oulu</t>
-  </si>
-  <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
-    <t>BULGARIA 1</t>
-  </si>
-  <si>
-    <t>CSKA Sofia x PFC Levski Sofia</t>
-  </si>
-  <si>
     <t>11:00:00</t>
   </si>
   <si>
     <t>SCOTLAND 2</t>
   </si>
   <si>
-    <t>Arbroath x Partick</t>
-  </si>
-  <si>
-    <t>NORWAY 1</t>
-  </si>
-  <si>
-    <t>Fredrikstad x Viking</t>
+    <t>Airdrieonians x Ayr</t>
   </si>
   <si>
     <t>13:00:00</t>
@@ -125,19 +104,37 @@
     <t>Bologna x Roma</t>
   </si>
   <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Felgueiras x Leiria</t>
+    <t>SWITZERLAND 1</t>
+  </si>
+  <si>
+    <t>Grasshoppers Zurich x Luzern</t>
+  </si>
+  <si>
+    <t>SLOVAKIA 1</t>
+  </si>
+  <si>
+    <t>KFC Komarno x MFk Skalica</t>
+  </si>
+  <si>
+    <t>Zemplin x Podbrezova</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Burgos x Deportivo</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>Thun x Lugano</t>
   </si>
   <si>
     <t>P2</t>
-  </si>
-  <si>
-    <t>Queens Park x Dunfermline</t>
   </si>
   <si>
     <t>15:45:00</t>
@@ -489,14 +486,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -539,9 +536,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -563,14 +557,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -579,7 +571,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>49.210526315789473</v>
+        <v>40.652173913043484</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -593,35 +585,33 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H11" si="0">G3</f>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J11" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J12" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K11" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>49.210526315789473</v>
+        <f t="shared" ref="K3:K12" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>40.652173913043484</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -635,35 +625,33 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>58.4375</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -677,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -689,23 +677,21 @@
         <v>16</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H5">
+        <v>26</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -719,7 +705,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -731,23 +717,21 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
+        <v>17.5</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I6">
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>28.333333333333336</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -761,35 +745,33 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I7">
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>58.4375</v>
+        <v>27.5</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -803,35 +785,33 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I8">
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
+        <v>58.4375</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -842,41 +822,39 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>8.4</v>
-      </c>
-      <c r="I9">
+        <v>RED</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>63.175675675675684</v>
+        <v>-500</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -887,13 +865,13 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -902,19 +880,17 @@
         <v>8.6</v>
       </c>
       <c r="H10">
+        <v>8.6</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="0"/>
-        <v>8.6</v>
-      </c>
-      <c r="I10">
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
         <v>61.513157894736842</v>
       </c>
       <c r="L10">
@@ -926,40 +902,78 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
+      <c r="G11">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H11">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>64.930555555555557</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11">
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12">
         <v>7.4</v>
       </c>
-      <c r="H11">
+      <c r="H12">
+        <v>7.4</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="0"/>
-        <v>7.4</v>
-      </c>
-      <c r="I11">
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
         <v>73.046875</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>1</v>
       </c>
     </row>
